--- a/data/semanas/320_pe.xlsx
+++ b/data/semanas/320_pe.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL4"/>
+  <dimension ref="A1:AL15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,7 +629,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16946547</v>
+        <v>16969984</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -638,22 +638,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>443 - KAMEL SAAD 1 PE</t>
+          <t>608 - POSTO MONZA PE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Q041</t>
+          <t>Q001</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rodovia MS-164</t>
+          <t>Rodovia 163</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>101 - 1 - C</t>
+          <t>01 - C</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -668,12 +668,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>17/08/2026 09:03</t>
+          <t>17/08/2026 08:44</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>17/08/2026 09:23</t>
+          <t>17/08/2026 08:57</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -690,13 +690,13 @@
         </is>
       </c>
       <c r="N2" s="2" t="n">
-        <v>46251.37708333333</v>
+        <v>46251.36388888889</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>46251.39097222222</v>
+        <v>46251.37291666667</v>
       </c>
       <c r="P2" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="Q2" s="3" t="n">
         <v>46251</v>
@@ -714,7 +714,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W2" t="b">
         <v>0</v>
@@ -737,10 +737,10 @@
       </c>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF2" t="n">
-        <v>543</v>
+        <v>524</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16946548</v>
+        <v>16946547</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -779,17 +779,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Q036</t>
+          <t>Q041</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rua MONTE ALTO</t>
+          <t>Rodovia MS-164</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>121 - C</t>
+          <t>101 - 1 - C</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>17/08/2026 09:26</t>
+          <t>17/08/2026 09:03</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>17/08/2026 09:37</t>
+          <t>17/08/2026 09:23</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -826,13 +826,13 @@
         </is>
       </c>
       <c r="N3" s="2" t="n">
-        <v>46251.39305555556</v>
+        <v>46251.37708333333</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>46251.40069444444</v>
+        <v>46251.39097222222</v>
       </c>
       <c r="P3" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="Q3" s="3" t="n">
         <v>46251</v>
@@ -850,7 +850,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3" t="b">
         <v>0</v>
@@ -865,7 +865,7 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1380</v>
+        <v>1140</v>
       </c>
       <c r="AB3" t="b">
         <v>0</v>
@@ -878,7 +878,7 @@
         <v>9</v>
       </c>
       <c r="AF3" t="n">
-        <v>566</v>
+        <v>543</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>16946549</v>
+        <v>16969985</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -917,17 +917,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Q032</t>
+          <t>Q036</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rua MONTES CLAROS</t>
+          <t>Rua MONTE AZUL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>100 - C</t>
+          <t>193 - 2 - C</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -942,12 +942,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>17/08/2026 09:40</t>
+          <t>17/08/2026 09:24</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>17/08/2026 10:03</t>
+          <t>17/08/2026 09:37</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -964,13 +964,13 @@
         </is>
       </c>
       <c r="N4" s="2" t="n">
-        <v>46251.40277777778</v>
+        <v>46251.39166666667</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>46251.41875</v>
+        <v>46251.40069444444</v>
       </c>
       <c r="P4" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="Q4" s="3" t="n">
         <v>46251</v>
@@ -988,7 +988,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W4" t="b">
         <v>0</v>
@@ -1003,7 +1003,7 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>840</v>
+        <v>1260</v>
       </c>
       <c r="AB4" t="b">
         <v>0</v>
@@ -1016,7 +1016,7 @@
         <v>9</v>
       </c>
       <c r="AF4" t="n">
-        <v>580</v>
+        <v>564</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
@@ -1036,6 +1036,1524 @@
         <v>1</v>
       </c>
       <c r="AL4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>16946548</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>443 - KAMEL SAAD 1 PE</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Q036</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Rua MONTE ALTO</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>121 - C</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>17/08/2026 09:26</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>17/08/2026 09:37</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>46251.39305555556</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>46251.40069444444</v>
+      </c>
+      <c r="P5" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="R5" t="n">
+        <v>320</v>
+      </c>
+      <c r="S5" t="n">
+        <v>33</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="b">
+        <v>0</v>
+      </c>
+      <c r="W5" t="b">
+        <v>0</v>
+      </c>
+      <c r="X5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>566</v>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="AH5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>16995003</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>443 - KAMEL SAAD 1 PE</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Rua MONTE AZUL</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>347 - C</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>17/08/2026 09:38</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>17/08/2026 09:48</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>46251.40138888889</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>46251.40833333333</v>
+      </c>
+      <c r="P6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="R6" t="n">
+        <v>320</v>
+      </c>
+      <c r="S6" t="n">
+        <v>33</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="b">
+        <v>0</v>
+      </c>
+      <c r="W6" t="b">
+        <v>0</v>
+      </c>
+      <c r="X6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>720</v>
+      </c>
+      <c r="AB6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>578</v>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="AH6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>16946549</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>443 - KAMEL SAAD 1 PE</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Rua MONTES CLAROS</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>100 - C</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>17/08/2026 09:40</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>17/08/2026 10:03</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>46251.40277777778</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>46251.41875</v>
+      </c>
+      <c r="P7" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="R7" t="n">
+        <v>320</v>
+      </c>
+      <c r="S7" t="n">
+        <v>33</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="b">
+        <v>1</v>
+      </c>
+      <c r="W7" t="b">
+        <v>0</v>
+      </c>
+      <c r="X7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>580</v>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="AH7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>16995004</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>443 - KAMEL SAAD 1 PE</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Rua ALFENAS</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>18 - C</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>17/08/2026 09:51</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>17/08/2026 10:09</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>46251.41041666667</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>46251.42291666667</v>
+      </c>
+      <c r="P8" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="R8" t="n">
+        <v>320</v>
+      </c>
+      <c r="S8" t="n">
+        <v>33</v>
+      </c>
+      <c r="T8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="b">
+        <v>1</v>
+      </c>
+      <c r="W8" t="b">
+        <v>0</v>
+      </c>
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>660</v>
+      </c>
+      <c r="AB8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>591</v>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="AH8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>16995005</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>443 - KAMEL SAAD 1 PE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Avenida DA FLORA</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>3102 - C</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>17/08/2026 13:47</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>17/08/2026 13:57</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>46251.57430555556</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>46251.58125</v>
+      </c>
+      <c r="P9" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="R9" t="n">
+        <v>320</v>
+      </c>
+      <c r="S9" t="n">
+        <v>33</v>
+      </c>
+      <c r="T9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="b">
+        <v>0</v>
+      </c>
+      <c r="W9" t="b">
+        <v>0</v>
+      </c>
+      <c r="X9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>14160</v>
+      </c>
+      <c r="AB9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>827</v>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>16991707</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>443 - KAMEL SAAD 1 PE</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Q027</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Rua SALINAS</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>69 - 1 - C</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>17/08/2026 14:02</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>17/08/2026 14:30</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>46251.58472222222</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>46251.60416666666</v>
+      </c>
+      <c r="P10" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="R10" t="n">
+        <v>320</v>
+      </c>
+      <c r="S10" t="n">
+        <v>33</v>
+      </c>
+      <c r="T10" t="b">
+        <v>0</v>
+      </c>
+      <c r="U10" t="b">
+        <v>0</v>
+      </c>
+      <c r="V10" t="b">
+        <v>1</v>
+      </c>
+      <c r="W10" t="b">
+        <v>0</v>
+      </c>
+      <c r="X10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>842</v>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>16995006</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>442 - JARDIM INDEPENDENCIA - PE</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Q006</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Avenida DAS FLORES</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>218 - C</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>17/08/2026 14:31</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>17/08/2026 14:55</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>46251.60486111111</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>46251.62152777778</v>
+      </c>
+      <c r="P11" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="R11" t="n">
+        <v>320</v>
+      </c>
+      <c r="S11" t="n">
+        <v>33</v>
+      </c>
+      <c r="T11" t="b">
+        <v>0</v>
+      </c>
+      <c r="U11" t="b">
+        <v>0</v>
+      </c>
+      <c r="V11" t="b">
+        <v>1</v>
+      </c>
+      <c r="W11" t="b">
+        <v>0</v>
+      </c>
+      <c r="X11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1740</v>
+      </c>
+      <c r="AB11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>871</v>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>16995007</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>445 - IVONE PE</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Q016</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Rua GALILEU GALILEI</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>593 - C</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>17/08/2026 15:11</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>17/08/2026 15:36</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>46251.63263888889</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>46251.65</v>
+      </c>
+      <c r="P12" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q12" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="R12" t="n">
+        <v>320</v>
+      </c>
+      <c r="S12" t="n">
+        <v>33</v>
+      </c>
+      <c r="T12" t="b">
+        <v>0</v>
+      </c>
+      <c r="U12" t="b">
+        <v>0</v>
+      </c>
+      <c r="V12" t="b">
+        <v>1</v>
+      </c>
+      <c r="W12" t="b">
+        <v>0</v>
+      </c>
+      <c r="X12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2400</v>
+      </c>
+      <c r="AB12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>911</v>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>16991708</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>446 - GUY VILELA - PE</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Q014</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Rua VITAL BRASIL</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1863 - 1 - C</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>17/08/2026 15:43</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>17/08/2026 15:53</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>46251.65486111111</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>46251.66180555556</v>
+      </c>
+      <c r="P13" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q13" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="R13" t="n">
+        <v>320</v>
+      </c>
+      <c r="S13" t="n">
+        <v>33</v>
+      </c>
+      <c r="T13" t="b">
+        <v>0</v>
+      </c>
+      <c r="U13" t="b">
+        <v>0</v>
+      </c>
+      <c r="V13" t="b">
+        <v>0</v>
+      </c>
+      <c r="W13" t="b">
+        <v>0</v>
+      </c>
+      <c r="X13" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1920</v>
+      </c>
+      <c r="AB13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>943</v>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>16995008</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>443 - KAMEL SAAD 1 PE</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Q029</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Rua DOS BEIJOS</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>418 - C</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>19/08/2026 08:12</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>19/08/2026 09:13</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>46253.34166666667</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>46253.38402777778</v>
+      </c>
+      <c r="P14" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q14" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="R14" t="n">
+        <v>320</v>
+      </c>
+      <c r="S14" t="n">
+        <v>33</v>
+      </c>
+      <c r="T14" t="b">
+        <v>0</v>
+      </c>
+      <c r="U14" t="b">
+        <v>1</v>
+      </c>
+      <c r="V14" t="b">
+        <v>1</v>
+      </c>
+      <c r="W14" t="b">
+        <v>0</v>
+      </c>
+      <c r="X14" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>145740</v>
+      </c>
+      <c r="AB14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>492</v>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="AH14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>16995009</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>442 - JARDIM INDEPENDENCIA - PE</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Q018</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Rua CAIABIS</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>172 - C</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>19/08/2026 09:18</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>19/08/2026 09:31</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>46253.3875</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>46253.39652777778</v>
+      </c>
+      <c r="P15" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q15" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="R15" t="n">
+        <v>320</v>
+      </c>
+      <c r="S15" t="n">
+        <v>33</v>
+      </c>
+      <c r="T15" t="b">
+        <v>0</v>
+      </c>
+      <c r="U15" t="b">
+        <v>0</v>
+      </c>
+      <c r="V15" t="b">
+        <v>0</v>
+      </c>
+      <c r="W15" t="b">
+        <v>0</v>
+      </c>
+      <c r="X15" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3960</v>
+      </c>
+      <c r="AB15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>558</v>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="AH15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL15" t="b">
         <v>0</v>
       </c>
     </row>

--- a/data/semanas/320_pe.xlsx
+++ b/data/semanas/320_pe.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL15"/>
+  <dimension ref="A1:AL29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2554,6 +2554,1938 @@
         <v>1</v>
       </c>
       <c r="AL15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>17034314</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>440 - IBIRAPUERA - PE</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Q002</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Rodovia MS-164</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1182 - 3 - C</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>19/08/2026 09:46</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>19/08/2026 09:57</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>46253.40694444445</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>46253.41458333333</v>
+      </c>
+      <c r="P16" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q16" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="R16" t="n">
+        <v>320</v>
+      </c>
+      <c r="S16" t="n">
+        <v>33</v>
+      </c>
+      <c r="T16" t="b">
+        <v>0</v>
+      </c>
+      <c r="U16" t="b">
+        <v>0</v>
+      </c>
+      <c r="V16" t="b">
+        <v>0</v>
+      </c>
+      <c r="W16" t="b">
+        <v>0</v>
+      </c>
+      <c r="X16" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1680</v>
+      </c>
+      <c r="AB16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>586</v>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="AH16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>17034315</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>440 - IBIRAPUERA - PE</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Q003</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Rodovia MS-164</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1300 - C</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>19/08/2026 09:58</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>19/08/2026 10:19</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>46253.41527777778</v>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>46253.42986111111</v>
+      </c>
+      <c r="P17" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="R17" t="n">
+        <v>320</v>
+      </c>
+      <c r="S17" t="n">
+        <v>33</v>
+      </c>
+      <c r="T17" t="b">
+        <v>0</v>
+      </c>
+      <c r="U17" t="b">
+        <v>0</v>
+      </c>
+      <c r="V17" t="b">
+        <v>1</v>
+      </c>
+      <c r="W17" t="b">
+        <v>0</v>
+      </c>
+      <c r="X17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>720</v>
+      </c>
+      <c r="AB17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>598</v>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="AH17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17037596</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>435 - JARDIM PRIMOR- PE</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Q025</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Avenida DA FLORA</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>57 - 01 - C</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20/08/2026 14:04</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>20/08/2026 14:17</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>46254.58611111111</v>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>46254.59513888889</v>
+      </c>
+      <c r="P18" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q18" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="R18" t="n">
+        <v>320</v>
+      </c>
+      <c r="S18" t="n">
+        <v>33</v>
+      </c>
+      <c r="T18" t="b">
+        <v>0</v>
+      </c>
+      <c r="U18" t="b">
+        <v>0</v>
+      </c>
+      <c r="V18" t="b">
+        <v>0</v>
+      </c>
+      <c r="W18" t="b">
+        <v>0</v>
+      </c>
+      <c r="X18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>101160</v>
+      </c>
+      <c r="AB18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>844</v>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17037597</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>435 - JARDIM PRIMOR- PE</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Q021</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Rua SALGADO FILHO</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>32 - 2 - C</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20/08/2026 14:18</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>20/08/2026 14:32</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>46254.59583333333</v>
+      </c>
+      <c r="O19" s="2" t="n">
+        <v>46254.60555555556</v>
+      </c>
+      <c r="P19" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q19" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="R19" t="n">
+        <v>320</v>
+      </c>
+      <c r="S19" t="n">
+        <v>33</v>
+      </c>
+      <c r="T19" t="b">
+        <v>0</v>
+      </c>
+      <c r="U19" t="b">
+        <v>0</v>
+      </c>
+      <c r="V19" t="b">
+        <v>0</v>
+      </c>
+      <c r="W19" t="b">
+        <v>0</v>
+      </c>
+      <c r="X19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>840</v>
+      </c>
+      <c r="AB19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>858</v>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>17037598</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>435 - JARDIM PRIMOR- PE</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Q019</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Avenida DA FLORA</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>113 - 3 - C</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20/08/2026 14:34</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>20/08/2026 14:58</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>46254.60694444444</v>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>46254.62361111111</v>
+      </c>
+      <c r="P20" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q20" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="R20" t="n">
+        <v>320</v>
+      </c>
+      <c r="S20" t="n">
+        <v>33</v>
+      </c>
+      <c r="T20" t="b">
+        <v>0</v>
+      </c>
+      <c r="U20" t="b">
+        <v>0</v>
+      </c>
+      <c r="V20" t="b">
+        <v>1</v>
+      </c>
+      <c r="W20" t="b">
+        <v>0</v>
+      </c>
+      <c r="X20" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>960</v>
+      </c>
+      <c r="AB20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>874</v>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>17039926</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>438 - PLANALTO - PE</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Q044</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Rua DAS PERDIZES</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>3046 - C</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>20/08/2026 14:41</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>20/08/2026 14:51</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>46254.61180555556</v>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>46254.61875</v>
+      </c>
+      <c r="P21" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q21" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="R21" t="n">
+        <v>320</v>
+      </c>
+      <c r="S21" t="n">
+        <v>33</v>
+      </c>
+      <c r="T21" t="b">
+        <v>0</v>
+      </c>
+      <c r="U21" t="b">
+        <v>0</v>
+      </c>
+      <c r="V21" t="b">
+        <v>0</v>
+      </c>
+      <c r="W21" t="b">
+        <v>0</v>
+      </c>
+      <c r="X21" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>420</v>
+      </c>
+      <c r="AB21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>881</v>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>17039927</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>427 - JAMIL SALDANHA DERZI PE</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Q033</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Rua MANGUEIRA</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>892 - 1 - C</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>20/08/2026 14:55</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:03</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>46254.62152777778</v>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>46254.62708333333</v>
+      </c>
+      <c r="P22" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="R22" t="n">
+        <v>320</v>
+      </c>
+      <c r="S22" t="n">
+        <v>33</v>
+      </c>
+      <c r="T22" t="b">
+        <v>0</v>
+      </c>
+      <c r="U22" t="b">
+        <v>0</v>
+      </c>
+      <c r="V22" t="b">
+        <v>0</v>
+      </c>
+      <c r="W22" t="b">
+        <v>0</v>
+      </c>
+      <c r="X22" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>840</v>
+      </c>
+      <c r="AB22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>895</v>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>17037599</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>419 - CENTRO 5 PE</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Q008</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Avenida ANTONIO JOAO</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2643 - OU</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:00</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:11</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>46254.625</v>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>46254.63263888889</v>
+      </c>
+      <c r="P23" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q23" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="R23" t="n">
+        <v>320</v>
+      </c>
+      <c r="S23" t="n">
+        <v>33</v>
+      </c>
+      <c r="T23" t="b">
+        <v>0</v>
+      </c>
+      <c r="U23" t="b">
+        <v>0</v>
+      </c>
+      <c r="V23" t="b">
+        <v>0</v>
+      </c>
+      <c r="W23" t="b">
+        <v>0</v>
+      </c>
+      <c r="X23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>300</v>
+      </c>
+      <c r="AB23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>900</v>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>17039928</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>434 - VILA AUREA - PE</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Q011</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Rua PEDRO ANGELO DA ROSA</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>816 - C</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:09</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:15</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>46254.63125</v>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>46254.63541666666</v>
+      </c>
+      <c r="P24" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q24" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="R24" t="n">
+        <v>320</v>
+      </c>
+      <c r="S24" t="n">
+        <v>33</v>
+      </c>
+      <c r="T24" t="b">
+        <v>0</v>
+      </c>
+      <c r="U24" t="b">
+        <v>0</v>
+      </c>
+      <c r="V24" t="b">
+        <v>0</v>
+      </c>
+      <c r="W24" t="b">
+        <v>0</v>
+      </c>
+      <c r="X24" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>540</v>
+      </c>
+      <c r="AB24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>909</v>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>17039929</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>420 - FERROVIARIA- PE</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Q013</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Travessa PROJETADA 06 FERROVIARIA</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>160 - C</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:18</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:28</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>46254.6375</v>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>46254.64444444444</v>
+      </c>
+      <c r="P25" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q25" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="R25" t="n">
+        <v>320</v>
+      </c>
+      <c r="S25" t="n">
+        <v>33</v>
+      </c>
+      <c r="T25" t="b">
+        <v>0</v>
+      </c>
+      <c r="U25" t="b">
+        <v>0</v>
+      </c>
+      <c r="V25" t="b">
+        <v>0</v>
+      </c>
+      <c r="W25" t="b">
+        <v>0</v>
+      </c>
+      <c r="X25" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>540</v>
+      </c>
+      <c r="AB25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>918</v>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>17037600</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>419 - CENTRO 5 PE</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Q002</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Rua GENERAL OSORIO</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>1840 - C</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:21</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:35</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>46254.63958333333</v>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>46254.64930555555</v>
+      </c>
+      <c r="P26" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q26" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="R26" t="n">
+        <v>320</v>
+      </c>
+      <c r="S26" t="n">
+        <v>33</v>
+      </c>
+      <c r="T26" t="b">
+        <v>0</v>
+      </c>
+      <c r="U26" t="b">
+        <v>0</v>
+      </c>
+      <c r="V26" t="b">
+        <v>0</v>
+      </c>
+      <c r="W26" t="b">
+        <v>0</v>
+      </c>
+      <c r="X26" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>921</v>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>17039930</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>421 - IPANEMA - PE</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Q028</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Travessa DOS PODERES</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>81 - OU</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:35</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:50</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>46254.64930555555</v>
+      </c>
+      <c r="O27" s="2" t="n">
+        <v>46254.65972222222</v>
+      </c>
+      <c r="P27" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q27" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="R27" t="n">
+        <v>320</v>
+      </c>
+      <c r="S27" t="n">
+        <v>33</v>
+      </c>
+      <c r="T27" t="b">
+        <v>0</v>
+      </c>
+      <c r="U27" t="b">
+        <v>0</v>
+      </c>
+      <c r="V27" t="b">
+        <v>0</v>
+      </c>
+      <c r="W27" t="b">
+        <v>0</v>
+      </c>
+      <c r="X27" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>840</v>
+      </c>
+      <c r="AB27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>935</v>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>17037601</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>419 - CENTRO 5 PE</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Q020</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Rua 15 DENOVEMBRO</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>67 - C</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:36</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:49</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>46254.65</v>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>46254.65902777778</v>
+      </c>
+      <c r="P28" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q28" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="R28" t="n">
+        <v>320</v>
+      </c>
+      <c r="S28" t="n">
+        <v>33</v>
+      </c>
+      <c r="T28" t="b">
+        <v>0</v>
+      </c>
+      <c r="U28" t="b">
+        <v>0</v>
+      </c>
+      <c r="V28" t="b">
+        <v>0</v>
+      </c>
+      <c r="W28" t="b">
+        <v>0</v>
+      </c>
+      <c r="X28" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>936</v>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>17039931</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>421 - IPANEMA - PE</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Rua JORGE ROBERTO SALOMAO</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>1400 - 5 - C</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:53</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>20/08/2026 16:00</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>46254.66180555556</v>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v>46254.66666666666</v>
+      </c>
+      <c r="P29" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q29" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="R29" t="n">
+        <v>320</v>
+      </c>
+      <c r="S29" t="n">
+        <v>33</v>
+      </c>
+      <c r="T29" t="b">
+        <v>0</v>
+      </c>
+      <c r="U29" t="b">
+        <v>0</v>
+      </c>
+      <c r="V29" t="b">
+        <v>0</v>
+      </c>
+      <c r="W29" t="b">
+        <v>0</v>
+      </c>
+      <c r="X29" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1020</v>
+      </c>
+      <c r="AB29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>953</v>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL29" t="b">
         <v>0</v>
       </c>
     </row>

--- a/data/semanas/320_pe.xlsx
+++ b/data/semanas/320_pe.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL29"/>
+  <dimension ref="A1:AL32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4486,6 +4486,420 @@
         <v>1</v>
       </c>
       <c r="AL29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>17055386</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>439 - BOSQUE CARANDÁ PE</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Q028</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Avenida PERPETUO SOCORRO</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>03 - OU</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>21/08/2026 08:17</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>21/08/2026 08:33</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>46255.34513888889</v>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v>46255.35625</v>
+      </c>
+      <c r="P30" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q30" s="3" t="n">
+        <v>46255</v>
+      </c>
+      <c r="R30" t="n">
+        <v>320</v>
+      </c>
+      <c r="S30" t="n">
+        <v>33</v>
+      </c>
+      <c r="T30" t="b">
+        <v>0</v>
+      </c>
+      <c r="U30" t="b">
+        <v>0</v>
+      </c>
+      <c r="V30" t="b">
+        <v>1</v>
+      </c>
+      <c r="W30" t="b">
+        <v>0</v>
+      </c>
+      <c r="X30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>59040</v>
+      </c>
+      <c r="AB30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>497</v>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="AH30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>17055387</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>434 - VILA AUREA - PE</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Q024</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Rua PEDRO ANGELO DA ROSA</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>81 - 6 - OU</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>21/08/2026 08:45</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>21/08/2026 09:09</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>46255.36458333334</v>
+      </c>
+      <c r="O31" s="2" t="n">
+        <v>46255.38125</v>
+      </c>
+      <c r="P31" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q31" s="3" t="n">
+        <v>46255</v>
+      </c>
+      <c r="R31" t="n">
+        <v>320</v>
+      </c>
+      <c r="S31" t="n">
+        <v>33</v>
+      </c>
+      <c r="T31" t="b">
+        <v>0</v>
+      </c>
+      <c r="U31" t="b">
+        <v>0</v>
+      </c>
+      <c r="V31" t="b">
+        <v>1</v>
+      </c>
+      <c r="W31" t="b">
+        <v>0</v>
+      </c>
+      <c r="X31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1680</v>
+      </c>
+      <c r="AB31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>525</v>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="AH31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>17055388</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>421 - IPANEMA - PE</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Q030</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Rua JORGE ROBERTO SALOMAO</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>01 - OU</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>21/08/2026 09:23</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>21/08/2026 09:56</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>46255.39097222222</v>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>46255.41388888889</v>
+      </c>
+      <c r="P32" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q32" s="3" t="n">
+        <v>46255</v>
+      </c>
+      <c r="R32" t="n">
+        <v>320</v>
+      </c>
+      <c r="S32" t="n">
+        <v>33</v>
+      </c>
+      <c r="T32" t="b">
+        <v>0</v>
+      </c>
+      <c r="U32" t="b">
+        <v>1</v>
+      </c>
+      <c r="V32" t="b">
+        <v>1</v>
+      </c>
+      <c r="W32" t="b">
+        <v>0</v>
+      </c>
+      <c r="X32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2280</v>
+      </c>
+      <c r="AB32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>563</v>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="AH32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL32" t="b">
         <v>0</v>
       </c>
     </row>
